--- a/datasets/election_data/data/output/eu_positions.xlsx
+++ b/datasets/election_data/data/output/eu_positions.xlsx
@@ -6874,7 +6874,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
+          <t>https://campaign.ecpm.info/wp-content/themes/ecpm-eu24/assets/pdf/ECPM-Political-Manifesto.pdf</t>
         </is>
       </c>
     </row>
